--- a/data/trending_integrated_20261021_14.xlsx
+++ b/data/trending_integrated_20261021_14.xlsx
@@ -578,7 +578,7 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10595147757</v>
+        <v>10596172757</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14890</v>
+        <v>14630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.26%</t>
+          <t>'+21.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>95660397400</v>
+        <v>97694645830</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1765</v>
+        <v>9830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.12%</t>
+          <t>'+13.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.66</v>
       </c>
       <c r="E4" t="n">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="F4" t="n">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>341</v>
+        <v>437</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6899999999999999</v>
+        <v>5.34</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1520</v>
+        <v>8650</v>
       </c>
       <c r="K4" t="n">
-        <v>1132</v>
+        <v>9010</v>
       </c>
       <c r="L4" t="n">
-        <v>1952</v>
+        <v>9910</v>
       </c>
       <c r="M4" t="n">
-        <v>1115</v>
+        <v>8790</v>
       </c>
       <c r="N4" t="n">
-        <v>0.57</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>66299424877</v>
+        <v>40954648990</v>
       </c>
       <c r="P4" t="n">
-        <v>3980</v>
+        <v>14940</v>
       </c>
       <c r="Q4" t="n">
-        <v>1115</v>
+        <v>5390</v>
       </c>
       <c r="R4" t="n">
-        <v>-148000</v>
+        <v>257000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>푸드나무, 그린하버의 경영권 인수(주당 3500원) 공시 확인. 3연상 기대감 및 40% 이상 수익률 언급.</t>
+          <t>미국 중복 상장 시도 실패 언급 속, 테슬라 관련 긍정적 전망과 함께 1만원대 안착 기대감 표현. 거래량 증가 및 족쇄 풀렸다는 표현으로 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '경영권', '공시']</t>
+          <t>['중복상장', '테슬라', '1만원대']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9740</v>
+        <v>10880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.60%</t>
+          <t>'+11.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.66</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="G5" t="n">
-        <v>399</v>
+        <v>507</v>
       </c>
       <c r="H5" t="n">
-        <v>5.34</v>
+        <v>1.28</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8650</v>
+        <v>9770</v>
       </c>
       <c r="K5" t="n">
-        <v>9010</v>
+        <v>10320</v>
       </c>
       <c r="L5" t="n">
-        <v>9860</v>
+        <v>11690</v>
       </c>
       <c r="M5" t="n">
-        <v>8790</v>
+        <v>9690</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>37461405790</v>
+        <v>284731926990</v>
       </c>
       <c r="P5" t="n">
-        <v>14940</v>
+        <v>11690</v>
       </c>
       <c r="Q5" t="n">
-        <v>5390</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>257000</v>
+        <v>-13000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-98000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 중복상장 시도 실패 및 국내 주가 관리 부진 속에서 1만원대 안착 전망과 상장 철회 가능성이 제기됩니다.</t>
+          <t>AI 데이터센터 수주 잔고 1조 돌파 언급에도 불구하고 단기 고점 및 급락 가능성 우려 제기. 로봇주 전반의 상승세 속에서 일부 투자자들의 신중론.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['중복상장', '주가관리', '상장철회']</t>
+          <t>['AI', '데이터센터', '급락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10920</v>
+        <v>1691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.77%</t>
+          <t>'+11.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="F6" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="G6" t="n">
-        <v>487</v>
+        <v>355</v>
       </c>
       <c r="H6" t="n">
-        <v>1.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9770</v>
+        <v>1520</v>
       </c>
       <c r="K6" t="n">
-        <v>10320</v>
+        <v>1132</v>
       </c>
       <c r="L6" t="n">
-        <v>11690</v>
+        <v>1952</v>
       </c>
       <c r="M6" t="n">
-        <v>9690</v>
+        <v>1115</v>
       </c>
       <c r="N6" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="O6" t="n">
-        <v>282971897815</v>
+        <v>67791762876</v>
       </c>
       <c r="P6" t="n">
-        <v>11690</v>
+        <v>3980</v>
       </c>
       <c r="Q6" t="n">
-        <v>2270</v>
+        <v>1115</v>
       </c>
       <c r="R6" t="n">
-        <v>-13000</v>
+        <v>-148000</v>
       </c>
       <c r="S6" t="n">
-        <v>-98000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주 잔고 1조 대비 낮은 시가총액에 대한 기대감과 함께 신고가 및 급등 가능성이 제기됩니다.</t>
+          <t>그린하버의 355억 경영권 인수 공시 기반으로 3연상 및 5천원 이상 안착 전망. 인수 가격 대비 주가 상승 기대감 높은 상황.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['인공지능', '수주잔고', '로봇주']</t>
+          <t>['인수', '경영권', '3연상']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13790</v>
+        <v>13770</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.16%</t>
+          <t>'+8.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="H7" t="n">
         <v>3.15</v>
@@ -1070,7 +1070,7 @@
         <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>121100622450</v>
+        <v>122098124905</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>222500</v>
+        <v>220500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.20%</t>
+          <t>'+4.26%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G8" t="n">
-        <v>1696</v>
+        <v>1680</v>
       </c>
       <c r="H8" t="n">
         <v>46.08</v>
@@ -1162,7 +1162,7 @@
         <v>46.04</v>
       </c>
       <c r="O8" t="n">
-        <v>2730575724750</v>
+        <v>2814362159750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 중국 반도체 퇴출 결정 속보와 함께 개인 매수 금지, 기관 동반 매수 중이라는 상반된 전망이 혼재합니다.</t>
+          <t>미국 중국 반도체 퇴출 결정 속보와 함께 개인 투자자들의 부정적 언급, 일부 긍정적 전망 혼재. 외인, 기관 동반 매수 언급 있으나 전반적인 논조는 혼조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '퇴출', '매수']</t>
+          <t>['반도체', '외인', '기관']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1278000</v>
+        <v>1272000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.50%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="G9" t="n">
-        <v>1546</v>
+        <v>1560</v>
       </c>
       <c r="H9" t="n">
         <v>48.77</v>
@@ -1254,7 +1254,7 @@
         <v>48.81</v>
       </c>
       <c r="O9" t="n">
-        <v>3987830859000</v>
+        <v>4132891941000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 주가 하락에 대한 불만이 제기되며, 단기적인 반등 가능성에 대한 회의적인 시각이 나타납니다.</t>
+          <t>자사주 매입 완료 소식과 함께 정치적 이슈(이재명)에 대한 강한 부정적 언급이 주를 이룸. 주가 하락에 대한 불만과 함께 단기 반등 기대 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주매입', '주주친화책', '반도체']</t>
+          <t>['자사주매입', '이재명', '단기반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14720</v>
+        <v>14690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+3.74%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1346,7 +1346,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>28686559300</v>
+        <v>29084293445</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17760</v>
+        <v>17750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H11" t="n">
         <v>27.78</v>
@@ -1438,7 +1438,7 @@
         <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>38541593235</v>
+        <v>39558875375</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2900</v>
+        <v>2910</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.11%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
         <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H12" t="n">
         <v>5.82</v>
@@ -1530,7 +1530,7 @@
         <v>5.91</v>
       </c>
       <c r="O12" t="n">
-        <v>17090311604</v>
+        <v>17134292584</v>
       </c>
       <c r="P12" t="n">
         <v>19950</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7400</v>
+        <v>7360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.79%</t>
+          <t>'+1.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="H13" t="n">
         <v>25.45</v>
@@ -1622,7 +1622,7 @@
         <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>12388846935</v>
+        <v>12870008675</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63600</v>
+        <v>63300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.27%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G14" t="n">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="H14" t="n">
         <v>22.23</v>
@@ -1714,7 +1714,7 @@
         <v>22.29</v>
       </c>
       <c r="O14" t="n">
-        <v>72434767600</v>
+        <v>74142863600</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1559</v>
+        <v>1550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.89%</t>
+          <t>'-1.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1800,13 +1800,13 @@
         <v>1715</v>
       </c>
       <c r="M15" t="n">
-        <v>1558</v>
+        <v>1550</v>
       </c>
       <c r="N15" t="n">
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>30509768526</v>
+        <v>31024180366</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3085</v>
+        <v>3090</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>10771153189</v>
+        <v>10854350146</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4275</v>
+        <v>4250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.67%</t>
+          <t>'-8.21%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>22846923602</v>
+        <v>23998488328</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>

--- a/data/trending_integrated_20261021_14.xlsx
+++ b/data/trending_integrated_20261021_14.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10596172757</v>
+        <v>10605995257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14630</v>
+        <v>14660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.11%</t>
+          <t>'+21.36%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
         <v>129</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>97694645830</v>
+        <v>98488395760</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -711,7 +711,7 @@
         <v>12030</v>
       </c>
       <c r="R3" t="n">
-        <v>162000</v>
+        <v>135000</v>
       </c>
       <c r="S3" t="n">
         <v>1000</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9830</v>
+        <v>9770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.64%</t>
+          <t>'+12.95%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.66</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="H4" t="n">
         <v>5.34</v>
@@ -794,7 +794,7 @@
         <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>40954648990</v>
+        <v>43469098065</v>
       </c>
       <c r="P4" t="n">
         <v>14940</v>
@@ -803,14 +803,14 @@
         <v>5390</v>
       </c>
       <c r="R4" t="n">
-        <v>257000</v>
+        <v>370000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 중복 상장 시도 실패 언급 속, 테슬라 관련 긍정적 전망과 함께 1만원대 안착 기대감 표현. 거래량 증가 및 족쇄 풀렸다는 표현으로 상승 기대.</t>
+          <t>미국 중복 상장 시도 실패 관련 내용. 1만원대 안착 전망 및 테슬라 연관 호재 언급. 일부 투자자는 부정적 의견 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['중복상장', '테슬라', '1만원대']</t>
+          <t>['중복상장', '테슬라', '안착']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10880</v>
+        <v>10860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.36%</t>
+          <t>'+11.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F5" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G5" t="n">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>284731926990</v>
+        <v>286938001290</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -895,23 +895,23 @@
         <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>-13000</v>
+        <v>-83000</v>
       </c>
       <c r="S5" t="n">
-        <v>-98000</v>
+        <v>-114000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AI 데이터센터 수주 잔고 1조 돌파 언급에도 불구하고 단기 고점 및 급락 가능성 우려 제기. 로봇주 전반의 상승세 속에서 일부 투자자들의 신중론.</t>
+          <t>인공지능 데이터센터 수주 잔고 1조원 돌파 관련 분석. 로봇주 섹터 내 대장주 역할 기대감 및 신고가 재돌파 가능성 언급. 단기 고점 및 급락 가능성 우려도 공존.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '데이터센터', '급락']</t>
+          <t>['수주잔고', '인공지능', '로봇주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.25%</t>
+          <t>'+10.99%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="F6" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G6" t="n">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="H6" t="n">
         <v>0.6899999999999999</v>
@@ -978,7 +978,7 @@
         <v>0.57</v>
       </c>
       <c r="O6" t="n">
-        <v>67791762876</v>
+        <v>69473938795</v>
       </c>
       <c r="P6" t="n">
         <v>3980</v>
@@ -987,14 +987,14 @@
         <v>1115</v>
       </c>
       <c r="R6" t="n">
-        <v>-148000</v>
+        <v>-184000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>그린하버의 355억 경영권 인수 공시 기반으로 3연상 및 5천원 이상 안착 전망. 인수 가격 대비 주가 상승 기대감 높은 상황.</t>
+          <t>푸드나무 경영권 인수 관련 공시 및 기사 언급. 주당 3500원 인수 가격 기반 긍정적 주가 전망 제시. 3연상 기대감도 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['인수', '경영권', '3연상']</t>
+          <t>['경영권인수', '공시', '주가전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13770</v>
+        <v>13950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.00%</t>
+          <t>'+9.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="H7" t="n">
         <v>3.15</v>
@@ -1070,7 +1070,7 @@
         <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>122098124905</v>
+        <v>123625025290</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1079,10 +1079,10 @@
         <v>1640</v>
       </c>
       <c r="R7" t="n">
-        <v>177000</v>
+        <v>87000</v>
       </c>
       <c r="S7" t="n">
-        <v>137000</v>
+        <v>157000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>220500</v>
+        <v>1282000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.26%</t>
+          <t>'+4.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="G8" t="n">
-        <v>1680</v>
+        <v>1593</v>
       </c>
       <c r="H8" t="n">
-        <v>46.08</v>
+        <v>48.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>211500</v>
+        <v>1223000</v>
       </c>
       <c r="K8" t="n">
-        <v>217000</v>
+        <v>1260000</v>
       </c>
       <c r="L8" t="n">
-        <v>228000</v>
+        <v>1329000</v>
       </c>
       <c r="M8" t="n">
-        <v>217000</v>
+        <v>1254000</v>
       </c>
       <c r="N8" t="n">
-        <v>46.04</v>
+        <v>48.81</v>
       </c>
       <c r="O8" t="n">
-        <v>2814362159750</v>
+        <v>4215679480500</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R8" t="n">
-        <v>2736000</v>
+        <v>419000</v>
       </c>
       <c r="S8" t="n">
-        <v>497000</v>
+        <v>37000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 중국 반도체 퇴출 결정 속보와 함께 개인 투자자들의 부정적 언급, 일부 긍정적 전망 혼재. 외인, 기관 동반 매수 언급 있으나 전반적인 논조는 혼조.</t>
+          <t>자사주 매입 종료 및 솔리다임 관련 언급. 정치적 이슈와 연관 지어 부정적 전망 다수 제시. 메모리 반도체 호재 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '외인', '기관']</t>
+          <t>['자사주매입', '솔리다임', '메모리']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1272000</v>
+        <v>221000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+4.49%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="G9" t="n">
-        <v>1560</v>
+        <v>1602</v>
       </c>
       <c r="H9" t="n">
-        <v>48.77</v>
+        <v>46.08</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1223000</v>
+        <v>211500</v>
       </c>
       <c r="K9" t="n">
-        <v>1260000</v>
+        <v>217000</v>
       </c>
       <c r="L9" t="n">
-        <v>1329000</v>
+        <v>228000</v>
       </c>
       <c r="M9" t="n">
-        <v>1254000</v>
+        <v>217000</v>
       </c>
       <c r="N9" t="n">
-        <v>48.81</v>
+        <v>46.04</v>
       </c>
       <c r="O9" t="n">
-        <v>4132891941000</v>
+        <v>2868604369750</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>468000</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>326000</v>
+        <v>1733000</v>
       </c>
       <c r="S9" t="n">
-        <v>57000</v>
+        <v>400000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>자사주 매입 완료 소식과 함께 정치적 이슈(이재명)에 대한 강한 부정적 언급이 주를 이룸. 주가 하락에 대한 불만과 함께 단기 반등 기대 언급.</t>
+          <t>미국 중국 반도체 퇴출 결정 관련 뉴스 언급. 일부 투자자는 부정적 전망 제시하나, 다른 투자자는 긍정적 전망 및 강력 매수 의견 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주매입', '이재명', '단기반등']</t>
+          <t>['반도체', '퇴출', '매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14690</v>
+        <v>14730</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.74%</t>
+          <t>'+4.03%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F10" t="n">
         <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H10" t="n">
         <v>9.82</v>
@@ -1346,7 +1346,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>29084293445</v>
+        <v>29542058445</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1355,10 +1355,10 @@
         <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>356000</v>
+        <v>353000</v>
       </c>
       <c r="S10" t="n">
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17750</v>
+        <v>17740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.48%</t>
+          <t>'+2.42%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="H11" t="n">
         <v>27.78</v>
@@ -1438,7 +1438,7 @@
         <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>39558875375</v>
+        <v>40544143225</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1447,10 +1447,10 @@
         <v>17170</v>
       </c>
       <c r="R11" t="n">
-        <v>488000</v>
+        <v>616000</v>
       </c>
       <c r="S11" t="n">
-        <v>13000</v>
+        <v>66000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2910</v>
+        <v>2905</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H12" t="n">
         <v>5.82</v>
@@ -1530,7 +1530,7 @@
         <v>5.91</v>
       </c>
       <c r="O12" t="n">
-        <v>17134292584</v>
+        <v>17196710299</v>
       </c>
       <c r="P12" t="n">
         <v>19950</v>
@@ -1539,7 +1539,7 @@
         <v>1913</v>
       </c>
       <c r="R12" t="n">
-        <v>-1060000</v>
+        <v>-1051000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7360</v>
+        <v>7390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.24%</t>
+          <t>'+1.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="H13" t="n">
         <v>25.45</v>
@@ -1622,7 +1622,7 @@
         <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>12870008675</v>
+        <v>13105313210</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1631,10 +1631,10 @@
         <v>7190</v>
       </c>
       <c r="R13" t="n">
-        <v>268000</v>
+        <v>264000</v>
       </c>
       <c r="S13" t="n">
-        <v>-4000</v>
+        <v>-15000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63300</v>
+        <v>63400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G14" t="n">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="H14" t="n">
         <v>22.23</v>
@@ -1714,7 +1714,7 @@
         <v>22.29</v>
       </c>
       <c r="O14" t="n">
-        <v>74142863600</v>
+        <v>78027607700</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1723,10 +1723,10 @@
         <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-59000</v>
+        <v>9000</v>
       </c>
       <c r="S14" t="n">
-        <v>25000</v>
+        <v>19000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1774,13 +1774,13 @@
         <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1800,13 +1800,13 @@
         <v>1715</v>
       </c>
       <c r="M15" t="n">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="N15" t="n">
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>31024180366</v>
+        <v>31474099112</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1815,7 +1815,7 @@
         <v>890</v>
       </c>
       <c r="R15" t="n">
-        <v>-797000</v>
+        <v>-738000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3090</v>
+        <v>3100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.48%</t>
+          <t>'-4.17%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.73</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>10854350146</v>
+        <v>11006304821</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1907,7 +1907,7 @@
         <v>2500</v>
       </c>
       <c r="R16" t="n">
-        <v>-129000</v>
+        <v>-127000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4250</v>
+        <v>4290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-8.21%</t>
+          <t>'-7.34%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" t="n">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>23998488328</v>
+        <v>24433040915</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>
@@ -1999,10 +1999,10 @@
         <v>2930</v>
       </c>
       <c r="R17" t="n">
-        <v>-1386000</v>
+        <v>-1400000</v>
       </c>
       <c r="S17" t="n">
-        <v>-462000</v>
+        <v>-607000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261021_14.xlsx
+++ b/data/trending_integrated_20261021_14.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10605995257</v>
+        <v>10607062757</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14660</v>
+        <v>14800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.36%</t>
+          <t>'+22.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
         <v>129</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>98488395760</v>
+        <v>100140819790</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9770</v>
+        <v>10020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.95%</t>
+          <t>'+15.84%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.66</v>
       </c>
       <c r="E4" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G4" t="n">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="H4" t="n">
         <v>5.34</v>
@@ -785,7 +785,7 @@
         <v>9010</v>
       </c>
       <c r="L4" t="n">
-        <v>9910</v>
+        <v>10100</v>
       </c>
       <c r="M4" t="n">
         <v>8790</v>
@@ -794,7 +794,7 @@
         <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>43469098065</v>
+        <v>46838328450</v>
       </c>
       <c r="P4" t="n">
         <v>14940</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 중복 상장 시도 실패 관련 내용. 1만원대 안착 전망 및 테슬라 연관 호재 언급. 일부 투자자는 부정적 의견 제시.</t>
+          <t>미국 중복 상장 시도 실패 후 국내 주가 관리 이슈. 1만원 안착 전망 및 테슬라 관련 호재 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['중복상장', '테슬라', '안착']</t>
+          <t>['중복상장', '주가관리', '테슬라']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10860</v>
+        <v>10870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.16%</t>
+          <t>'+11.26%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F5" t="n">
         <v>136</v>
       </c>
       <c r="G5" t="n">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>286938001290</v>
+        <v>288687881370</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1687</v>
+        <v>14060</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.99%</t>
+          <t>'+10.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>376</v>
+        <v>519</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1520</v>
+        <v>12750</v>
       </c>
       <c r="K6" t="n">
-        <v>1132</v>
+        <v>13080</v>
       </c>
       <c r="L6" t="n">
-        <v>1952</v>
+        <v>14290</v>
       </c>
       <c r="M6" t="n">
-        <v>1115</v>
+        <v>12680</v>
       </c>
       <c r="N6" t="n">
-        <v>0.57</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>69473938795</v>
+        <v>126595266455</v>
       </c>
       <c r="P6" t="n">
-        <v>3980</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1115</v>
+        <v>1640</v>
       </c>
       <c r="R6" t="n">
-        <v>-184000</v>
+        <v>87000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>푸드나무 경영권 인수 관련 공시 및 기사 언급. 주당 3500원 인수 가격 기반 긍정적 주가 전망 제시. 3연상 기대감도 존재.</t>
+          <t>미국 AI 데이터센터향 광케이블 2차 물량 공급 개시 공시를 바탕으로 숏커버 및 2만원 이상 상승에 대한 기대감이 높습니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['경영권인수', '공시', '주가전망']</t>
+          <t>['광케이블', '공시', 'AI데이터센터']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,91 +1011,91 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13950</v>
+        <v>1627</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.41%</t>
+          <t>'+7.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E7" t="n">
+        <v>252</v>
+      </c>
+      <c r="F7" t="n">
+        <v>123</v>
+      </c>
+      <c r="G7" t="n">
+        <v>400</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1132</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1115</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O7" t="n">
+        <v>70868490064</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3980</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1115</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-184000</v>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>86</v>
-      </c>
-      <c r="F7" t="n">
-        <v>61</v>
-      </c>
-      <c r="G7" t="n">
-        <v>501</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>12750</v>
-      </c>
-      <c r="K7" t="n">
-        <v>13080</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14290</v>
-      </c>
-      <c r="M7" t="n">
-        <v>12680</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O7" t="n">
-        <v>123625025290</v>
-      </c>
-      <c r="P7" t="n">
-        <v>31500</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1640</v>
-      </c>
-      <c r="R7" t="n">
-        <v>87000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>157000</v>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터향 광케이블 2차 물량 공급 개시 공시를 바탕으로 숏커버 및 2만원 이상 상승에 대한 기대감이 높습니다.</t>
+          <t>경영권 인수 공시 확인. 주당 3500원 인수 조건 하에 주가 상승 기대감 형성. 3연상 가능성 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광케이블', '공시', 'AI데이터센터']</t>
+          <t>['경영권인수', '공시', '주가상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1282000</v>
+        <v>1286000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.82%</t>
+          <t>'+5.15%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G8" t="n">
-        <v>1593</v>
+        <v>1564</v>
       </c>
       <c r="H8" t="n">
         <v>48.77</v>
@@ -1162,7 +1162,7 @@
         <v>48.81</v>
       </c>
       <c r="O8" t="n">
-        <v>4215679480500</v>
+        <v>4276578834500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1171,23 +1171,23 @@
         <v>468000</v>
       </c>
       <c r="R8" t="n">
-        <v>419000</v>
+        <v>430000</v>
       </c>
       <c r="S8" t="n">
         <v>37000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 종료 및 솔리다임 관련 언급. 정치적 이슈와 연관 지어 부정적 전망 다수 제시. 메모리 반도체 호재 기대감도 일부 존재.</t>
+          <t>자사주 매입 종료 후 정치적 이슈와 함께 주가 하락 우려. 단기 급락 후 회복 가능성 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '솔리다임', '메모리']</t>
+          <t>['자사주매입', '정치', '하락']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>221000</v>
+        <v>221250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.49%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G9" t="n">
-        <v>1602</v>
+        <v>1656</v>
       </c>
       <c r="H9" t="n">
         <v>46.08</v>
@@ -1254,7 +1254,7 @@
         <v>46.04</v>
       </c>
       <c r="O9" t="n">
-        <v>2868604369750</v>
+        <v>2907434796500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1263,14 +1263,14 @@
         <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>1733000</v>
+        <v>1750000</v>
       </c>
       <c r="S9" t="n">
         <v>400000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 중국 반도체 퇴출 결정 관련 뉴스 언급. 일부 투자자는 부정적 전망 제시하나, 다른 투자자는 긍정적 전망 및 강력 매수 의견 제시.</t>
+          <t>반도체 퇴출 결정 관련 이슈 및 정치적 발언 혼재. 주가 반등 기대와 하락 우려 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '퇴출', '매수']</t>
+          <t>['반도체', '퇴출', '정치']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14730</v>
+        <v>14740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.03%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H10" t="n">
         <v>9.82</v>
@@ -1346,7 +1346,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>29542058445</v>
+        <v>29829791315</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1355,7 +1355,7 @@
         <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>353000</v>
+        <v>359000</v>
       </c>
       <c r="S10" t="n">
         <v>7000</v>
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17740</v>
+        <v>2920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.42%</t>
+          <t>'+2.82%</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>86</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>263</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2840</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3100</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3300</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2855</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="O11" t="n">
+        <v>17265540634</v>
+      </c>
+      <c r="P11" t="n">
+        <v>19950</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1913</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1051000</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>95</v>
-      </c>
-      <c r="F11" t="n">
-        <v>54</v>
-      </c>
-      <c r="G11" t="n">
-        <v>235</v>
-      </c>
-      <c r="H11" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>17320</v>
-      </c>
-      <c r="K11" t="n">
-        <v>17480</v>
-      </c>
-      <c r="L11" t="n">
-        <v>17840</v>
-      </c>
-      <c r="M11" t="n">
-        <v>17170</v>
-      </c>
-      <c r="N11" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="O11" t="n">
-        <v>40544143225</v>
-      </c>
-      <c r="P11" t="n">
-        <v>35350</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>17170</v>
-      </c>
-      <c r="R11" t="n">
-        <v>616000</v>
-      </c>
-      <c r="S11" t="n">
-        <v>66000</v>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>민주당 및 이재명 정부에 대한 비판과 함께 조선, 방산, 원전 섹터의 전반적인 부진 및 주가 하락에 대한 우려가 제기됩니다.</t>
+          <t>공매도 세력에 대한 강한 비판과 주가 조작 의혹 제기, 그리고 외인 갭 띄우기 후 매도에 대한 불만이 팽배하며, 부정적 전망이 우세합니다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치비판', '섹터부진', '주가전망']</t>
+          <t>['공매도', '주가조작', '외인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2905</v>
+        <v>17750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.29%</t>
+          <t>'+2.48%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="H12" t="n">
-        <v>5.82</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2840</v>
+        <v>17320</v>
       </c>
       <c r="K12" t="n">
-        <v>3100</v>
+        <v>17480</v>
       </c>
       <c r="L12" t="n">
-        <v>3300</v>
+        <v>17840</v>
       </c>
       <c r="M12" t="n">
-        <v>2855</v>
+        <v>17170</v>
       </c>
       <c r="N12" t="n">
-        <v>5.91</v>
+        <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>17196710299</v>
+        <v>41085374610</v>
       </c>
       <c r="P12" t="n">
-        <v>19950</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1913</v>
+        <v>17170</v>
       </c>
       <c r="R12" t="n">
-        <v>-1051000</v>
+        <v>640000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 강한 비판과 주가 조작 의혹 제기, 그리고 외인 갭 띄우기 후 매도에 대한 불만이 팽배하며, 부정적 전망이 우세합니다.</t>
+          <t>민주당 및 이재명 정부에 대한 비판과 함께 조선, 방산, 원전 섹터의 전반적인 부진 및 주가 하락에 대한 우려가 제기됩니다.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '주가조작', '외인']</t>
+          <t>['정치비판', '섹터부진', '주가전망']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
         <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="H13" t="n">
         <v>25.45</v>
@@ -1622,7 +1622,7 @@
         <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>13105313210</v>
+        <v>13320136770</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1631,7 +1631,7 @@
         <v>7190</v>
       </c>
       <c r="R13" t="n">
-        <v>264000</v>
+        <v>272000</v>
       </c>
       <c r="S13" t="n">
         <v>-15000</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63400</v>
+        <v>63500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G14" t="n">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="H14" t="n">
         <v>22.23</v>
@@ -1714,7 +1714,7 @@
         <v>22.29</v>
       </c>
       <c r="O14" t="n">
-        <v>78027607700</v>
+        <v>79504570050</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1723,7 +1723,7 @@
         <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>9000</v>
+        <v>-13000</v>
       </c>
       <c r="S14" t="n">
         <v>19000</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.46%</t>
+          <t>'-1.65%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1800,13 +1800,13 @@
         <v>1715</v>
       </c>
       <c r="M15" t="n">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="N15" t="n">
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>31474099112</v>
+        <v>31800215954</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3100</v>
+        <v>3090</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.17%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.73</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>11006304821</v>
+        <v>11080670901</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4290</v>
+        <v>4280</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.34%</t>
+          <t>'-7.56%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>69</v>
       </c>
       <c r="G17" t="n">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>24433040915</v>
+        <v>24708555003</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>
@@ -1999,7 +1999,7 @@
         <v>2930</v>
       </c>
       <c r="R17" t="n">
-        <v>-1400000</v>
+        <v>-1408000</v>
       </c>
       <c r="S17" t="n">
         <v>-607000</v>

--- a/data/trending_integrated_20261021_14.xlsx
+++ b/data/trending_integrated_20261021_14.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10607062757</v>
+        <v>10614250257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14800</v>
+        <v>14790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.52%</t>
+          <t>'+22.43%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>100140819790</v>
+        <v>102220475735</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10020</v>
+        <v>10270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.84%</t>
+          <t>'+18.73%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.66</v>
       </c>
       <c r="E4" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F4" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="H4" t="n">
         <v>5.34</v>
@@ -785,7 +785,7 @@
         <v>9010</v>
       </c>
       <c r="L4" t="n">
-        <v>10100</v>
+        <v>10290</v>
       </c>
       <c r="M4" t="n">
         <v>8790</v>
@@ -794,7 +794,7 @@
         <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>46838328450</v>
+        <v>53581801935</v>
       </c>
       <c r="P4" t="n">
         <v>14940</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 중복 상장 시도 실패 후 국내 주가 관리 이슈. 1만원 안착 전망 및 테슬라 관련 호재 기대.</t>
+          <t>미국 중복 상장 시도 실패 및 국내 주가 관리 논란 속 1만원대 안착 전망. 테슬라 관련 호재 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10870</v>
+        <v>10930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.26%</t>
+          <t>'+11.87%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F5" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G5" t="n">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>288687881370</v>
+        <v>291297150285</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주 잔고 1조원 돌파 관련 분석. 로봇주 섹터 내 대장주 역할 기대감 및 신고가 재돌파 가능성 언급. 단기 고점 및 급락 가능성 우려도 공존.</t>
+          <t>인공지능 데이터센터 수주 잔고 1조원 돌파. 로봇주 강세 및 신고가 경신 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['수주잔고', '인공지능', '로봇주']</t>
+          <t>['인공지능', '수주', '로봇주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14060</v>
+        <v>14030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.27%</t>
+          <t>'+10.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
@@ -978,7 +978,7 @@
         <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>126595266455</v>
+        <v>128028771180</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1627</v>
+        <v>1281000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.04%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>252</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>506</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>1543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6899999999999999</v>
+        <v>48.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1520</v>
+        <v>1223000</v>
       </c>
       <c r="K7" t="n">
-        <v>1132</v>
+        <v>1260000</v>
       </c>
       <c r="L7" t="n">
-        <v>1952</v>
+        <v>1329000</v>
       </c>
       <c r="M7" t="n">
-        <v>1115</v>
+        <v>1254000</v>
       </c>
       <c r="N7" t="n">
-        <v>0.57</v>
+        <v>48.81</v>
       </c>
       <c r="O7" t="n">
-        <v>70868490064</v>
+        <v>4366666092000</v>
       </c>
       <c r="P7" t="n">
-        <v>3980</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1115</v>
+        <v>468000</v>
       </c>
       <c r="R7" t="n">
-        <v>-184000</v>
+        <v>430000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>경영권 인수 공시 확인. 주당 3500원 인수 조건 하에 주가 상승 기대감 형성. 3연상 가능성 제기.</t>
+          <t>정치적 이슈와 맞물려 주가 하락 지속. 메모리 반등 및 주주 친화책 기대감 있으나 단기 하락 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['경영권인수', '공시', '주가상승']</t>
+          <t>['메모리', '주주친화', '하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1286000</v>
+        <v>221000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.15%</t>
+          <t>'+4.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="G8" t="n">
-        <v>1564</v>
+        <v>1687</v>
       </c>
       <c r="H8" t="n">
-        <v>48.77</v>
+        <v>46.08</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1223000</v>
+        <v>211500</v>
       </c>
       <c r="K8" t="n">
-        <v>1260000</v>
+        <v>217000</v>
       </c>
       <c r="L8" t="n">
-        <v>1329000</v>
+        <v>228000</v>
       </c>
       <c r="M8" t="n">
-        <v>1254000</v>
+        <v>217000</v>
       </c>
       <c r="N8" t="n">
-        <v>48.81</v>
+        <v>46.04</v>
       </c>
       <c r="O8" t="n">
-        <v>4276578834500</v>
+        <v>2958686139000</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>468000</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>430000</v>
+        <v>1750000</v>
       </c>
       <c r="S8" t="n">
-        <v>37000</v>
+        <v>400000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 종료 후 정치적 이슈와 함께 주가 하락 우려. 단기 급락 후 회복 가능성 제기.</t>
+          <t>반도체 섹터 퇴출 관련 루머 및 정치적 발언으로 인한 혼조세. 단기적 상승 기대와 하락 전망 혼재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '정치', '하락']</t>
+          <t>['반도체', '퇴출', '전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>221250</v>
+        <v>14720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+3.95%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>515</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>1656</v>
+        <v>260</v>
       </c>
       <c r="H9" t="n">
-        <v>46.08</v>
+        <v>9.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>211500</v>
+        <v>14160</v>
       </c>
       <c r="K9" t="n">
-        <v>217000</v>
+        <v>14340</v>
       </c>
       <c r="L9" t="n">
-        <v>228000</v>
+        <v>14830</v>
       </c>
       <c r="M9" t="n">
-        <v>217000</v>
+        <v>14340</v>
       </c>
       <c r="N9" t="n">
-        <v>46.04</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>2907434796500</v>
+        <v>30237937940</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>1750000</v>
+        <v>359000</v>
       </c>
       <c r="S9" t="n">
-        <v>400000</v>
+        <v>7000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 퇴출 결정 관련 이슈 및 정치적 발언 혼재. 주가 반등 기대와 하락 우려 혼재.</t>
+          <t>외국인 및 기관의 매수세 유입과 실적 우량주로서의 잠재력에 대한 긍정적 시각과 함께, 주가 조작 의혹 및 이재명 정부에 대한 비판이 존재합니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '퇴출', '정치']</t>
+          <t>['외인수급', '실적', '주가조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14740</v>
+        <v>1575</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.10%</t>
+          <t>'+3.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>121</v>
+        <v>262</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="G10" t="n">
-        <v>259</v>
+        <v>420</v>
       </c>
       <c r="H10" t="n">
-        <v>9.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14160</v>
+        <v>1520</v>
       </c>
       <c r="K10" t="n">
-        <v>14340</v>
+        <v>1132</v>
       </c>
       <c r="L10" t="n">
-        <v>14830</v>
+        <v>1952</v>
       </c>
       <c r="M10" t="n">
-        <v>14340</v>
+        <v>1115</v>
       </c>
       <c r="N10" t="n">
-        <v>9.779999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="O10" t="n">
-        <v>29829791315</v>
+        <v>73018373023</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>3980</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>1115</v>
       </c>
       <c r="R10" t="n">
-        <v>359000</v>
+        <v>-184000</v>
       </c>
       <c r="S10" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외국인 및 기관의 매수세 유입과 실적 우량주로서의 잠재력에 대한 긍정적 시각과 함께, 주가 조작 의혹 및 이재명 정부에 대한 비판이 존재합니다.</t>
+          <t>그린하버의 랭킹닭컴 경영권 인수 발표. 주당 3500원 인수 가격 및 추가 상승 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인수급', '실적', '주가조작']</t>
+          <t>['인수', '랭킹닭컴', '상승']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2920</v>
+        <v>2910</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F11" t="n">
         <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H11" t="n">
         <v>5.82</v>
@@ -1438,7 +1438,7 @@
         <v>5.91</v>
       </c>
       <c r="O11" t="n">
-        <v>17265540634</v>
+        <v>17324422159</v>
       </c>
       <c r="P11" t="n">
         <v>19950</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17750</v>
+        <v>17720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.48%</t>
+          <t>'+2.31%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>41085374610</v>
+        <v>41873427260</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7390</v>
+        <v>7360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.65%</t>
+          <t>'+1.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F13" t="n">
         <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H13" t="n">
         <v>25.45</v>
@@ -1622,7 +1622,7 @@
         <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>13320136770</v>
+        <v>13582597520</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63500</v>
+        <v>63200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.11%</t>
+          <t>'+0.64%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H14" t="n">
         <v>22.23</v>
@@ -1714,7 +1714,7 @@
         <v>22.29</v>
       </c>
       <c r="O14" t="n">
-        <v>79504570050</v>
+        <v>80953070300</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 섹터 상승 시 원전 전력 섹터 동반 상승 기대감과 함께 연기금 매도 및 외인 매도에 대한 불만이 제기됩니다.</t>
+          <t>원전 및 전력 섹터 상승 기대감 속에서의 혼조세. SMR 관련 사업 반영 지연 및 외인 매도 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1547</v>
+        <v>1552</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.65%</t>
+          <t>'-1.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F15" t="n">
         <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1800,13 +1800,13 @@
         <v>1715</v>
       </c>
       <c r="M15" t="n">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="N15" t="n">
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>31800215954</v>
+        <v>32014606852</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3090</v>
+        <v>3110</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.48%</t>
+          <t>'-3.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.73</v>
       </c>
       <c r="E16" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>11080670901</v>
+        <v>11204629691</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1958,13 +1958,13 @@
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>24708555003</v>
+        <v>24942930108</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>

--- a/data/trending_integrated_20261021_14.xlsx
+++ b/data/trending_integrated_20261021_14.xlsx
@@ -563,70 +563,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>형지엘리트</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2500</v>
+        <v>14850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.94%</t>
+          <t>'+22.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.15</v>
+        <v>-0.27</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>232</v>
+        <v>133</v>
       </c>
       <c r="H2" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1924</v>
+        <v>12080</v>
       </c>
       <c r="K2" t="n">
-        <v>2310</v>
+        <v>12280</v>
       </c>
       <c r="L2" t="n">
-        <v>2500</v>
+        <v>15640</v>
       </c>
       <c r="M2" t="n">
-        <v>2200</v>
+        <v>12280</v>
       </c>
       <c r="N2" t="n">
-        <v>0.79</v>
+        <v>0.27</v>
       </c>
       <c r="O2" t="n">
-        <v>10614250257</v>
+        <v>102997342600</v>
       </c>
       <c r="P2" t="n">
-        <v>2665</v>
+        <v>28800</v>
       </c>
       <c r="Q2" t="n">
-        <v>292</v>
+        <v>12030</v>
       </c>
       <c r="R2" t="n">
-        <v>-105000</v>
+        <v>135000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>역대 최대 매출 및 3년 새 2배 성장 전망. 퀀텀 점프 기대감으로 상한가 및 연상 기대.</t>
+          <t>엘리스 후속주로 부각되며 급등. 노광 장비 관련주.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['역대 최대 매출', '퀀텀 점프', '성장 전망']</t>
+          <t>['노광 장비', '엘리스', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,86 +648,86 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>093240</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14790</v>
+        <v>10220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.43%</t>
+          <t>'+18.15%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.27</v>
+        <v>-0.66</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="G3" t="n">
-        <v>134</v>
+        <v>537</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12080</v>
+        <v>8650</v>
       </c>
       <c r="K3" t="n">
-        <v>12280</v>
+        <v>9010</v>
       </c>
       <c r="L3" t="n">
-        <v>15640</v>
+        <v>10460</v>
       </c>
       <c r="M3" t="n">
-        <v>12280</v>
+        <v>8790</v>
       </c>
       <c r="N3" t="n">
-        <v>0.27</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>102220475735</v>
+        <v>60013606445</v>
       </c>
       <c r="P3" t="n">
-        <v>28800</v>
+        <v>14940</v>
       </c>
       <c r="Q3" t="n">
-        <v>12030</v>
+        <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>135000</v>
+        <v>370000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>엘리스 후속주로 부각되며 급등. 노광 장비 관련주.</t>
+          <t>미국 중복 상장 시도 실패 및 주가 관리 비판 속에서 1만원 안착 전망. 테슬라 연관 기대감 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['노광 장비', '엘리스', '급등']</t>
+          <t>['중복상장', '테슬라']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>형지엘리트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10270</v>
+        <v>2225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.73%</t>
+          <t>'+15.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.66</v>
+        <v>3.15</v>
       </c>
       <c r="E4" t="n">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>488</v>
+        <v>225</v>
       </c>
       <c r="H4" t="n">
-        <v>5.34</v>
+        <v>3.94</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8650</v>
+        <v>1924</v>
       </c>
       <c r="K4" t="n">
-        <v>9010</v>
+        <v>2310</v>
       </c>
       <c r="L4" t="n">
-        <v>10290</v>
+        <v>2500</v>
       </c>
       <c r="M4" t="n">
-        <v>8790</v>
+        <v>2155</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0.79</v>
       </c>
       <c r="O4" t="n">
-        <v>53581801935</v>
+        <v>12825320524</v>
       </c>
       <c r="P4" t="n">
-        <v>14940</v>
+        <v>2665</v>
       </c>
       <c r="Q4" t="n">
-        <v>5390</v>
+        <v>292</v>
       </c>
       <c r="R4" t="n">
-        <v>370000</v>
+        <v>-105000</v>
       </c>
       <c r="S4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 중복 상장 시도 실패 및 국내 주가 관리 논란 속 1만원대 안착 전망. 테슬라 관련 호재 기대.</t>
+          <t>역대 최대 매출 및 3년 새 2배 성장 전망. 퀀텀 점프 기대감으로 상한가 및 연상 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['중복상장', '주가관리', '테슬라']</t>
+          <t>['역대 최대 매출', '퀀텀 점프', '성장 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>093240</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10930</v>
+        <v>10970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.87%</t>
+          <t>'+12.28%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F5" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G5" t="n">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>291297150285</v>
+        <v>294512531095</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주 잔고 1조원 돌파. 로봇주 강세 및 신고가 경신 기대감.</t>
+          <t>인공지능 데이터센터 수주잔고 대비 낮은 시가총액 언급. 로봇주 섹터 내 강세 및 신고가 돌파 기대감 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['인공지능', '수주', '로봇주']</t>
+          <t>['수주잔고', '로봇주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14030</v>
+        <v>14120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.04%</t>
+          <t>'+10.75%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>533</v>
+        <v>562</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
@@ -978,7 +978,7 @@
         <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>128028771180</v>
+        <v>130458539190</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1281000</v>
+        <v>1289000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.74%</t>
+          <t>'+5.40%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="G7" t="n">
-        <v>1543</v>
+        <v>1555</v>
       </c>
       <c r="H7" t="n">
         <v>48.77</v>
@@ -1070,7 +1070,7 @@
         <v>48.81</v>
       </c>
       <c r="O7" t="n">
-        <v>4366666092000</v>
+        <v>4446779882000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 주가 하락 지속. 메모리 반등 및 주주 친화책 기대감 있으나 단기 하락 우려.</t>
+          <t>자사주 매입 종료 후 주가 하락 및 정치적 이슈와 연관된 부정적 전망. 메모리 업황 개선 기대감 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['메모리', '주주친화', '하락']</t>
+          <t>['자사주', '메모리']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>221000</v>
+        <v>1598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.49%</t>
+          <t>'+5.13%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>273</v>
       </c>
       <c r="F8" t="n">
-        <v>521</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>1687</v>
+        <v>448</v>
       </c>
       <c r="H8" t="n">
-        <v>46.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>211500</v>
+        <v>1520</v>
       </c>
       <c r="K8" t="n">
-        <v>217000</v>
+        <v>1132</v>
       </c>
       <c r="L8" t="n">
-        <v>228000</v>
+        <v>1952</v>
       </c>
       <c r="M8" t="n">
-        <v>217000</v>
+        <v>1115</v>
       </c>
       <c r="N8" t="n">
-        <v>46.04</v>
+        <v>0.57</v>
       </c>
       <c r="O8" t="n">
-        <v>2958686139000</v>
+        <v>75670632278</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>3980</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>1115</v>
       </c>
       <c r="R8" t="n">
-        <v>1750000</v>
+        <v>-184000</v>
       </c>
       <c r="S8" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>반도체 섹터 퇴출 관련 루머 및 정치적 발언으로 인한 혼조세. 단기적 상승 기대와 하락 전망 혼재.</t>
+          <t>그린하버의 경영권 인수 공시 확인. 인수 가격을 중심으로 향후 주가 상승 기대감이 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '퇴출', '전망']</t>
+          <t>['인수', '공시', '랭킹닭컴']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14720</v>
+        <v>221500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+4.73%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>525</v>
       </c>
       <c r="G9" t="n">
-        <v>260</v>
+        <v>1680</v>
       </c>
       <c r="H9" t="n">
-        <v>9.82</v>
+        <v>46.08</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14160</v>
+        <v>211500</v>
       </c>
       <c r="K9" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="L9" t="n">
-        <v>14830</v>
+        <v>228000</v>
       </c>
       <c r="M9" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="N9" t="n">
-        <v>9.779999999999999</v>
+        <v>46.04</v>
       </c>
       <c r="O9" t="n">
-        <v>30237937940</v>
+        <v>3001551332750</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>359000</v>
+        <v>1750000</v>
       </c>
       <c r="S9" t="n">
-        <v>7000</v>
+        <v>400000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인 및 기관의 매수세 유입과 실적 우량주로서의 잠재력에 대한 긍정적 시각과 함께, 주가 조작 의혹 및 이재명 정부에 대한 비판이 존재합니다.</t>
+          <t>정치적 이슈와 개인적 투자 경험을 바탕으로 한 혼재된 의견. 일부는 긍정적 전망을 제시하나, 근거는 불분명.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인수급', '실적', '주가조작']</t>
+          <t>['정치', '전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1575</v>
+        <v>14700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.62%</t>
+          <t>'+3.81%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>262</v>
+        <v>121</v>
       </c>
       <c r="F10" t="n">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>261</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1520</v>
+        <v>14160</v>
       </c>
       <c r="K10" t="n">
-        <v>1132</v>
+        <v>14340</v>
       </c>
       <c r="L10" t="n">
-        <v>1952</v>
+        <v>14830</v>
       </c>
       <c r="M10" t="n">
-        <v>1115</v>
+        <v>14340</v>
       </c>
       <c r="N10" t="n">
-        <v>0.57</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>73018373023</v>
+        <v>30563941225</v>
       </c>
       <c r="P10" t="n">
-        <v>3980</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>1115</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-184000</v>
+        <v>359000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>그린하버의 랭킹닭컴 경영권 인수 발표. 주당 3500원 인수 가격 및 추가 상승 기대감.</t>
+          <t>외국인 및 기관의 매수세 유입과 실적 우량주로서의 잠재력에 대한 긍정적 시각과 함께, 주가 조작 의혹 및 이재명 정부에 대한 비판이 존재합니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['인수', '랭킹닭컴', '상승']</t>
+          <t>['외인수급', '실적', '주가조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2910</v>
+        <v>2905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
         <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H11" t="n">
         <v>5.82</v>
@@ -1438,7 +1438,7 @@
         <v>5.91</v>
       </c>
       <c r="O11" t="n">
-        <v>17324422159</v>
+        <v>17410065264</v>
       </c>
       <c r="P11" t="n">
         <v>19950</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17720</v>
+        <v>17710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.31%</t>
+          <t>'+2.25%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>102</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>41873427260</v>
+        <v>42878576445</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7360</v>
+        <v>7330</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.24%</t>
+          <t>'+0.83%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="H13" t="n">
         <v>25.45</v>
@@ -1622,7 +1622,7 @@
         <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>13582597520</v>
+        <v>14048545365</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63200</v>
+        <v>63300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.64%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G14" t="n">
-        <v>531</v>
+        <v>583</v>
       </c>
       <c r="H14" t="n">
         <v>22.23</v>
@@ -1714,7 +1714,7 @@
         <v>22.29</v>
       </c>
       <c r="O14" t="n">
-        <v>80953070300</v>
+        <v>85077025850</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1552</v>
+        <v>1548</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.34%</t>
+          <t>'-1.59%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1806,7 +1806,7 @@
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>32014606852</v>
+        <v>32189163486</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1866,13 +1866,13 @@
         <v>-0.73</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F16" t="n">
         <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>11204629691</v>
+        <v>11335304121</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4280</v>
+        <v>4290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.56%</t>
+          <t>'-7.34%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>24942930108</v>
+        <v>25182655141</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>
